--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T13:48:48+00:00</t>
+    <t>2026-03-19T07:57:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T07:57:25+00:00</t>
+    <t>2026-03-19T11:47:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T11:47:55+00:00</t>
+    <t>2026-03-20T10:04:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T10:04:21+00:00</t>
+    <t>2026-03-20T11:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:14:53+00:00</t>
+    <t>2026-03-20T11:25:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:25:24+00:00</t>
+    <t>2026-03-20T11:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.1.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T11:48:45+00:00</t>
+    <t>2026-03-20T12:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T12:42:40+00:00</t>
+    <t>2026-03-20T12:57:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T12:57:31+00:00</t>
+    <t>2026-03-20T13:17:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.3</t>
+    <t>0.1.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:17:08+00:00</t>
+    <t>2026-04-10T11:25:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:25:48+00:00</t>
+    <t>2026-04-10T11:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:43:13+00:00</t>
+    <t>2026-04-10T11:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:51:44+00:00</t>
+    <t>2026-04-10T12:03:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:03:27+00:00</t>
+    <t>2026-04-10T12:17:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:17:42+00:00</t>
+    <t>2026-04-10T12:43:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:43:41+00:00</t>
+    <t>2026-04-10T12:51:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T12:51:31+00:00</t>
+    <t>2026-04-10T13:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.4</t>
+    <t>0.1.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:11:24+00:00</t>
+    <t>2026-04-13T12:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T12:24:04+00:00</t>
+    <t>2026-04-13T13:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.5</t>
+    <t>0.1.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T13:08:41+00:00</t>
+    <t>2026-04-15T12:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,7 +117,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>4</t>
+    <t>3</t>
   </si>
   <si>
     <t>Level</t>
@@ -160,15 +160,6 @@
   </si>
   <si>
     <t>enheter i spesialisthelsetjenesten</t>
-  </si>
-  <si>
-    <t>urn:oid:2.16.578.1.12.4.1.4.107</t>
-  </si>
-  <si>
-    <t>AKO</t>
-  </si>
-  <si>
-    <t>Apotekenes konsesjonsnummer</t>
   </si>
 </sst>
 </file>
@@ -474,7 +465,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -533,20 +524,6 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s" s="2">
-        <v>51</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/currentbuild/CodeSystem-organization-id-type-cs.xlsx
+++ b/currentbuild/CodeSystem-organization-id-type-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.6</t>
+    <t>0.1.7</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T12:03:39+00:00</t>
+    <t>2026-04-16T08:13:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
